--- a/excels/Originals/8_asses.masses_E8Proxy.xlsx
+++ b/excels/Originals/8_asses.masses_E8Proxy.xlsx
@@ -2025,7 +2025,7 @@
     <t>Eşek Gücü!</t>
   </si>
   <si>
-    <t>Ezelkracht!</t>
+    <t>Ezels Eerst!</t>
   </si>
   <si>
     <t>Per la Força dels Ases!</t>
